--- a/payroll/2026/excel/20260914-0915.xlsx
+++ b/payroll/2026/excel/20260914-0915.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5592EA-E664-4043-8A3C-76D992B13E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7350" yWindow="0" windowWidth="35850" windowHeight="20985" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
+    <workbookView xWindow="7350" yWindow="0" windowWidth="36105" windowHeight="20985" activeTab="1" xr2:uid="{7A907552-1C41-4484-ABB7-89D0B7E40110}"/>
   </bookViews>
   <sheets>
     <sheet name="产出" sheetId="1" r:id="rId1"/>
@@ -5980,8 +5980,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B37:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
